--- a/EdenCampus_PhD/05_papers/paper1/Table5_meteorological_summary.xlsx
+++ b/EdenCampus_PhD/05_papers/paper1/Table5_meteorological_summary.xlsx
@@ -515,7 +515,7 @@
         <v>9.4</v>
       </c>
       <c r="D6" t="n">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
   </sheetData>
